--- a/Protocols/Params/Mouse_Room_Params.xlsx
+++ b/Protocols/Params/Mouse_Room_Params.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MouseRoom\Desktop\HeadFixedBehavior\Params\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ss\Documents\repos\behaviour_rig\Params\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78227AEB-11A2-46F8-804E-D68F90745DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25125" windowHeight="12330"/>
+    <workbookView xWindow="2595" yWindow="2595" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Params" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="108">
   <si>
     <t>Subject</t>
   </si>
@@ -88,9 +89,6 @@
     <t>Arduino</t>
   </si>
   <si>
-    <t>Asym_Left</t>
-  </si>
-  <si>
     <t>Unilateral_Right</t>
   </si>
   <si>
@@ -232,22 +230,142 @@
     <t>SS01</t>
   </si>
   <si>
-    <t>SS02</t>
-  </si>
-  <si>
     <t>SS04</t>
   </si>
   <si>
+    <t>QP0176</t>
+  </si>
+  <si>
+    <t>PRO_ANTI</t>
+  </si>
+  <si>
+    <t>Blocks_15</t>
+  </si>
+  <si>
+    <t>Low_Anti_High_Pro</t>
+  </si>
+  <si>
+    <t>QP0177</t>
+  </si>
+  <si>
+    <t>Random_Alternation</t>
+  </si>
+  <si>
+    <t>QP0178</t>
+  </si>
+  <si>
+    <t>QP0179</t>
+  </si>
+  <si>
+    <t>QP0180</t>
+  </si>
+  <si>
+    <t>QP0191</t>
+  </si>
+  <si>
+    <t>QP0195</t>
+  </si>
+  <si>
+    <t>QP0196</t>
+  </si>
+  <si>
+    <t>QP0197</t>
+  </si>
+  <si>
+    <t>QP0198</t>
+  </si>
+  <si>
+    <t>QP0199</t>
+  </si>
+  <si>
+    <t>Blocks_30</t>
+  </si>
+  <si>
+    <t>QP0200</t>
+  </si>
+  <si>
+    <t>QP0201</t>
+  </si>
+  <si>
+    <t>QP0202</t>
+  </si>
+  <si>
+    <t>Low_Right_High_Left</t>
+  </si>
+  <si>
+    <t>QP0203</t>
+  </si>
+  <si>
+    <t>QP0204</t>
+  </si>
+  <si>
+    <t>QP0205</t>
+  </si>
+  <si>
+    <t>Pro_Only</t>
+  </si>
+  <si>
+    <t>QP0206</t>
+  </si>
+  <si>
+    <t>QP0207</t>
+  </si>
+  <si>
+    <t>Three_And_Three</t>
+  </si>
+  <si>
+    <t>QP0208</t>
+  </si>
+  <si>
+    <t>Anti_Only</t>
+  </si>
+  <si>
+    <t>Habituation</t>
+  </si>
+  <si>
+    <t>TEST_Habi</t>
+  </si>
+  <si>
+    <t>TEST_Lick</t>
+  </si>
+  <si>
+    <t>TEST_3N3</t>
+  </si>
+  <si>
+    <t>Lick_To_Release</t>
+  </si>
+  <si>
     <t>SS05</t>
   </si>
   <si>
-    <t>Habituation</t>
+    <t>SS06</t>
+  </si>
+  <si>
+    <t>SS07</t>
+  </si>
+  <si>
+    <t>SS08</t>
+  </si>
+  <si>
+    <t>SS09</t>
+  </si>
+  <si>
+    <t>SS10</t>
+  </si>
+  <si>
+    <t>SS11</t>
+  </si>
+  <si>
+    <t>SS12</t>
+  </si>
+  <si>
+    <t>SS13</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -301,7 +419,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -310,6 +428,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -623,8 +742,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AW6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AW36"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -669,7 +788,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -687,94 +806,94 @@
         <v>7</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>16</v>
       </c>
       <c r="P1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="R1" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="S1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="Y1" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="Z1" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AC1" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="AD1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AE1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="AF1" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="AG1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AH1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="AK1" s="1" t="s">
         <v>12</v>
       </c>
       <c r="AL1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AM1" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="AN1" s="1" t="s">
         <v>13</v>
@@ -783,198 +902,188 @@
         <v>14</v>
       </c>
       <c r="AP1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="AT1" s="1" t="s">
         <v>15</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:49" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>95</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="D2" t="e">
-        <f>#N/A</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E2" t="str">
-        <f>PROPER(FALSE)</f>
-        <v>False</v>
+        <v>#N/A</v>
+      </c>
+      <c r="E2" t="b">
+        <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G2" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="2">
-        <v>8</v>
-      </c>
-      <c r="I2" t="str">
-        <f t="shared" ref="I2:J2" si="0">PROPER(FALSE)</f>
-        <v>False</v>
-      </c>
-      <c r="J2" t="str">
-        <f t="shared" si="0"/>
-        <v>False</v>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>0</v>
       </c>
       <c r="K2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" t="s">
         <v>29</v>
       </c>
-      <c r="L2" t="s">
-        <v>30</v>
-      </c>
       <c r="M2" t="s">
-        <v>55</v>
-      </c>
-      <c r="N2" s="3">
-        <v>300</v>
-      </c>
-      <c r="O2" t="str">
-        <f>PROPER(FALSE)</f>
-        <v>False</v>
-      </c>
-      <c r="P2" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="3">
-        <v>30</v>
-      </c>
-      <c r="R2" s="3">
-        <v>1</v>
-      </c>
-      <c r="S2" t="str">
-        <f t="shared" ref="S2" si="1">PROPER(FALSE)</f>
-        <v>False</v>
-      </c>
-      <c r="T2" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="U2" s="3">
+        <v>54</v>
+      </c>
+      <c r="N2">
+        <v>300</v>
+      </c>
+      <c r="O2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>30</v>
+      </c>
+      <c r="R2">
+        <v>1.75</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0.8</v>
+      </c>
+      <c r="U2">
         <v>0.5</v>
       </c>
-      <c r="V2" t="str">
-        <f t="shared" ref="V2" si="2">PROPER(FALSE)</f>
-        <v>False</v>
-      </c>
-      <c r="W2" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="X2" s="3">
-        <v>50</v>
-      </c>
-      <c r="Y2" s="3">
-        <v>50</v>
-      </c>
-      <c r="Z2" s="3">
-        <v>2</v>
-      </c>
-      <c r="AA2" s="3">
-        <v>5</v>
-      </c>
-      <c r="AB2" s="3">
-        <v>10</v>
-      </c>
-      <c r="AC2" s="3">
-        <v>50</v>
-      </c>
-      <c r="AD2" s="3">
+      <c r="V2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0.8</v>
+      </c>
+      <c r="X2">
+        <v>50</v>
+      </c>
+      <c r="Y2">
+        <v>50</v>
+      </c>
+      <c r="Z2">
+        <v>10</v>
+      </c>
+      <c r="AA2">
+        <v>3</v>
+      </c>
+      <c r="AB2">
+        <v>10</v>
+      </c>
+      <c r="AC2">
+        <v>50</v>
+      </c>
+      <c r="AD2">
         <v>82</v>
       </c>
-      <c r="AE2" s="3">
-        <v>300</v>
-      </c>
-      <c r="AF2" s="3">
-        <v>30</v>
-      </c>
-      <c r="AG2" t="str">
-        <f>PROPER(TRUE)</f>
-        <v>True</v>
-      </c>
-      <c r="AH2" s="3">
+      <c r="AE2">
+        <v>300</v>
+      </c>
+      <c r="AF2">
+        <v>30</v>
+      </c>
+      <c r="AG2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH2">
         <v>20</v>
       </c>
-      <c r="AI2" s="3">
-        <v>2</v>
-      </c>
-      <c r="AJ2" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="AK2" t="str">
-        <f t="shared" ref="AK2" si="3">PROPER(FALSE)</f>
-        <v>False</v>
-      </c>
-      <c r="AL2" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="AM2" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AN2" s="5">
-        <v>30</v>
-      </c>
-      <c r="AO2" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP2" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="AQ2" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AR2" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="AS2" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="AT2" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="AV2" s="5" t="s">
-        <v>63</v>
+      <c r="AI2">
+        <v>3</v>
+      </c>
+      <c r="AJ2">
+        <v>0.8</v>
+      </c>
+      <c r="AK2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV2" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AW2" t="e">
-        <f>#N/A</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="3" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="D3" t="e">
         <v>#N/A</v>
@@ -988,8 +1097,8 @@
       <c r="G3" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="2">
-        <v>8</v>
+      <c r="H3">
+        <v>2</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -998,13 +1107,13 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" t="s">
         <v>29</v>
       </c>
-      <c r="L3" t="s">
-        <v>30</v>
-      </c>
       <c r="M3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N3">
         <v>300</v>
@@ -1019,7 +1128,7 @@
         <v>30</v>
       </c>
       <c r="R3">
-        <v>0.5</v>
+        <v>1.75</v>
       </c>
       <c r="S3" t="b">
         <v>0</v>
@@ -1117,13 +1226,13 @@
     </row>
     <row r="4" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>91</v>
       </c>
       <c r="D4" t="e">
         <v>#N/A</v>
@@ -1137,8 +1246,8 @@
       <c r="G4" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="2">
-        <v>8</v>
+      <c r="H4">
+        <v>2</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -1147,13 +1256,13 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L4" t="s">
         <v>29</v>
       </c>
-      <c r="L4" t="s">
-        <v>30</v>
-      </c>
       <c r="M4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N4">
         <v>300</v>
@@ -1168,7 +1277,7 @@
         <v>30</v>
       </c>
       <c r="R4">
-        <v>0.5</v>
+        <v>1.75</v>
       </c>
       <c r="S4" t="b">
         <v>0</v>
@@ -1264,21 +1373,21 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="5" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>66</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D5" t="e">
         <v>#N/A</v>
       </c>
       <c r="E5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="s">
         <v>10</v>
@@ -1296,138 +1405,139 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L5" t="s">
         <v>29</v>
       </c>
-      <c r="L5" t="s">
-        <v>30</v>
-      </c>
       <c r="M5" t="s">
-        <v>55</v>
-      </c>
-      <c r="N5">
+        <v>54</v>
+      </c>
+      <c r="N5" s="3">
         <v>300</v>
       </c>
       <c r="O5" t="b">
-        <v>1</v>
-      </c>
-      <c r="P5">
-        <v>1</v>
-      </c>
-      <c r="Q5">
-        <v>30</v>
-      </c>
-      <c r="R5">
-        <v>0.25</v>
+        <v>0</v>
+      </c>
+      <c r="P5" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>30</v>
+      </c>
+      <c r="R5" s="3">
+        <v>1</v>
       </c>
       <c r="S5" t="b">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0.8</v>
-      </c>
-      <c r="U5">
+      <c r="T5" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="U5" s="3">
         <v>0.5</v>
       </c>
       <c r="V5" t="b">
         <v>0</v>
       </c>
-      <c r="W5">
-        <v>0.8</v>
-      </c>
-      <c r="X5">
-        <v>50</v>
-      </c>
-      <c r="Y5">
-        <v>50</v>
-      </c>
-      <c r="Z5">
+      <c r="W5" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="X5" s="3">
+        <v>50</v>
+      </c>
+      <c r="Y5" s="3">
+        <v>50</v>
+      </c>
+      <c r="Z5" s="3">
         <v>2</v>
       </c>
-      <c r="AA5">
-        <v>3</v>
-      </c>
-      <c r="AB5">
-        <v>10</v>
-      </c>
-      <c r="AC5">
-        <v>50</v>
-      </c>
-      <c r="AD5">
+      <c r="AA5" s="3">
+        <v>5</v>
+      </c>
+      <c r="AB5" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC5" s="3">
+        <v>50</v>
+      </c>
+      <c r="AD5" s="3">
         <v>82</v>
       </c>
-      <c r="AE5">
-        <v>300</v>
-      </c>
-      <c r="AF5">
+      <c r="AE5" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF5" s="3">
         <v>30</v>
       </c>
       <c r="AG5" t="b">
         <v>1</v>
       </c>
-      <c r="AH5">
+      <c r="AH5" s="3">
         <v>20</v>
       </c>
-      <c r="AI5">
-        <v>3</v>
-      </c>
-      <c r="AJ5">
+      <c r="AI5" s="3">
+        <v>2</v>
+      </c>
+      <c r="AJ5" s="3">
         <v>0.8</v>
       </c>
       <c r="AK5" t="b">
         <v>0</v>
       </c>
-      <c r="AL5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AM5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AN5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AO5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AR5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AS5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AT5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV5" t="e">
-        <v>#N/A</v>
+      <c r="AL5" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="AM5" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN5" s="5">
+        <v>30</v>
+      </c>
+      <c r="AO5" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP5" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="AQ5" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR5" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="AS5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="AT5" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="AV5" s="5" t="s">
+        <v>62</v>
       </c>
       <c r="AW5" t="e">
+        <f>#N/A</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="6" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="D6" t="e">
         <v>#N/A</v>
       </c>
       <c r="E6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="s">
         <v>10</v>
@@ -1445,19 +1555,19 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
+        <v>28</v>
+      </c>
+      <c r="L6" t="s">
         <v>29</v>
       </c>
-      <c r="L6" t="s">
-        <v>30</v>
-      </c>
       <c r="M6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N6">
         <v>300</v>
       </c>
       <c r="O6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6">
         <v>1</v>
@@ -1466,7 +1576,7 @@
         <v>30</v>
       </c>
       <c r="R6">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="S6" t="b">
         <v>0</v>
@@ -1559,6 +1669,4639 @@
         <v>#N/A</v>
       </c>
       <c r="AW6" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="7" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="2">
+        <v>8</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" t="s">
+        <v>28</v>
+      </c>
+      <c r="L7" t="s">
+        <v>29</v>
+      </c>
+      <c r="M7" t="s">
+        <v>54</v>
+      </c>
+      <c r="N7">
+        <v>300</v>
+      </c>
+      <c r="O7" t="b">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>30</v>
+      </c>
+      <c r="R7">
+        <v>0.25</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0.8</v>
+      </c>
+      <c r="U7">
+        <v>0.5</v>
+      </c>
+      <c r="V7" t="b">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0.8</v>
+      </c>
+      <c r="X7">
+        <v>50</v>
+      </c>
+      <c r="Y7">
+        <v>50</v>
+      </c>
+      <c r="Z7">
+        <v>2</v>
+      </c>
+      <c r="AA7">
+        <v>3</v>
+      </c>
+      <c r="AB7">
+        <v>10</v>
+      </c>
+      <c r="AC7">
+        <v>50</v>
+      </c>
+      <c r="AD7">
+        <v>82</v>
+      </c>
+      <c r="AE7">
+        <v>300</v>
+      </c>
+      <c r="AF7">
+        <v>30</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH7">
+        <v>20</v>
+      </c>
+      <c r="AI7">
+        <v>3</v>
+      </c>
+      <c r="AJ7">
+        <v>0.8</v>
+      </c>
+      <c r="AK7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM7" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN7" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO7" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP7" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ7" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR7" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS7" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT7" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU7" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV7" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW7" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="8" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8">
+        <v>2</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M8" t="s">
+        <v>54</v>
+      </c>
+      <c r="N8">
+        <v>300</v>
+      </c>
+      <c r="O8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>30</v>
+      </c>
+      <c r="R8">
+        <v>1.75</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0.8</v>
+      </c>
+      <c r="U8">
+        <v>0.5</v>
+      </c>
+      <c r="V8" t="b">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0.8</v>
+      </c>
+      <c r="X8">
+        <v>50</v>
+      </c>
+      <c r="Y8">
+        <v>50</v>
+      </c>
+      <c r="Z8">
+        <v>2</v>
+      </c>
+      <c r="AA8">
+        <v>3</v>
+      </c>
+      <c r="AB8">
+        <v>10</v>
+      </c>
+      <c r="AC8">
+        <v>50</v>
+      </c>
+      <c r="AD8">
+        <v>82</v>
+      </c>
+      <c r="AE8">
+        <v>300</v>
+      </c>
+      <c r="AF8">
+        <v>30</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH8">
+        <v>20</v>
+      </c>
+      <c r="AI8">
+        <v>3</v>
+      </c>
+      <c r="AJ8">
+        <v>0.8</v>
+      </c>
+      <c r="AK8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW8" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="9" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" t="s">
+        <v>98</v>
+      </c>
+      <c r="D9" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9">
+        <v>2</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M9" t="s">
+        <v>54</v>
+      </c>
+      <c r="N9">
+        <v>300</v>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>30</v>
+      </c>
+      <c r="R9">
+        <v>1.75</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0.8</v>
+      </c>
+      <c r="U9">
+        <v>0.5</v>
+      </c>
+      <c r="V9" t="b">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0.8</v>
+      </c>
+      <c r="X9">
+        <v>50</v>
+      </c>
+      <c r="Y9">
+        <v>50</v>
+      </c>
+      <c r="Z9">
+        <v>2</v>
+      </c>
+      <c r="AA9">
+        <v>3</v>
+      </c>
+      <c r="AB9">
+        <v>10</v>
+      </c>
+      <c r="AC9">
+        <v>50</v>
+      </c>
+      <c r="AD9">
+        <v>82</v>
+      </c>
+      <c r="AE9">
+        <v>300</v>
+      </c>
+      <c r="AF9">
+        <v>30</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH9">
+        <v>20</v>
+      </c>
+      <c r="AI9">
+        <v>3</v>
+      </c>
+      <c r="AJ9">
+        <v>0.8</v>
+      </c>
+      <c r="AK9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM9" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN9" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO9" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP9" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ9" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR9" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS9" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT9" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU9" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV9" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW9" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="10" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10">
+        <v>2</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" t="s">
+        <v>28</v>
+      </c>
+      <c r="L10" t="s">
+        <v>29</v>
+      </c>
+      <c r="M10" t="s">
+        <v>54</v>
+      </c>
+      <c r="N10">
+        <v>300</v>
+      </c>
+      <c r="O10" t="b">
+        <v>1</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <v>30</v>
+      </c>
+      <c r="R10">
+        <v>1.75</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0.8</v>
+      </c>
+      <c r="U10">
+        <v>0.5</v>
+      </c>
+      <c r="V10" t="b">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0.8</v>
+      </c>
+      <c r="X10">
+        <v>50</v>
+      </c>
+      <c r="Y10">
+        <v>50</v>
+      </c>
+      <c r="Z10">
+        <v>2</v>
+      </c>
+      <c r="AA10">
+        <v>3</v>
+      </c>
+      <c r="AB10">
+        <v>10</v>
+      </c>
+      <c r="AC10">
+        <v>50</v>
+      </c>
+      <c r="AD10">
+        <v>82</v>
+      </c>
+      <c r="AE10">
+        <v>300</v>
+      </c>
+      <c r="AF10">
+        <v>30</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH10">
+        <v>20</v>
+      </c>
+      <c r="AI10">
+        <v>3</v>
+      </c>
+      <c r="AJ10">
+        <v>0.8</v>
+      </c>
+      <c r="AK10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW10" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="11" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" t="s">
+        <v>98</v>
+      </c>
+      <c r="D11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" t="s">
+        <v>9</v>
+      </c>
+      <c r="H11">
+        <v>2</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" t="s">
+        <v>28</v>
+      </c>
+      <c r="L11" t="s">
+        <v>29</v>
+      </c>
+      <c r="M11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N11">
+        <v>300</v>
+      </c>
+      <c r="O11" t="b">
+        <v>1</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
+        <v>30</v>
+      </c>
+      <c r="R11">
+        <v>1.75</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0.8</v>
+      </c>
+      <c r="U11">
+        <v>0.5</v>
+      </c>
+      <c r="V11" t="b">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0.8</v>
+      </c>
+      <c r="X11">
+        <v>50</v>
+      </c>
+      <c r="Y11">
+        <v>50</v>
+      </c>
+      <c r="Z11">
+        <v>2</v>
+      </c>
+      <c r="AA11">
+        <v>3</v>
+      </c>
+      <c r="AB11">
+        <v>10</v>
+      </c>
+      <c r="AC11">
+        <v>50</v>
+      </c>
+      <c r="AD11">
+        <v>82</v>
+      </c>
+      <c r="AE11">
+        <v>300</v>
+      </c>
+      <c r="AF11">
+        <v>30</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH11">
+        <v>20</v>
+      </c>
+      <c r="AI11">
+        <v>3</v>
+      </c>
+      <c r="AJ11">
+        <v>0.8</v>
+      </c>
+      <c r="AK11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW11" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="12" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D12" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E12" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12">
+        <v>2</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" t="s">
+        <v>28</v>
+      </c>
+      <c r="L12" t="s">
+        <v>29</v>
+      </c>
+      <c r="M12" t="s">
+        <v>54</v>
+      </c>
+      <c r="N12">
+        <v>300</v>
+      </c>
+      <c r="O12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="Q12">
+        <v>30</v>
+      </c>
+      <c r="R12">
+        <v>1.75</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0.8</v>
+      </c>
+      <c r="U12">
+        <v>0.5</v>
+      </c>
+      <c r="V12" t="b">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0.8</v>
+      </c>
+      <c r="X12">
+        <v>50</v>
+      </c>
+      <c r="Y12">
+        <v>50</v>
+      </c>
+      <c r="Z12">
+        <v>10</v>
+      </c>
+      <c r="AA12">
+        <v>3</v>
+      </c>
+      <c r="AB12">
+        <v>10</v>
+      </c>
+      <c r="AC12">
+        <v>50</v>
+      </c>
+      <c r="AD12">
+        <v>82</v>
+      </c>
+      <c r="AE12">
+        <v>300</v>
+      </c>
+      <c r="AF12">
+        <v>30</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH12">
+        <v>20</v>
+      </c>
+      <c r="AI12">
+        <v>3</v>
+      </c>
+      <c r="AJ12">
+        <v>0.8</v>
+      </c>
+      <c r="AK12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM12" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN12" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO12" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP12" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ12" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR12" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS12" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT12" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU12" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV12" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW12" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E13" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" t="s">
+        <v>9</v>
+      </c>
+      <c r="H13">
+        <v>2</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L13" t="s">
+        <v>29</v>
+      </c>
+      <c r="M13" t="s">
+        <v>54</v>
+      </c>
+      <c r="N13">
+        <v>300</v>
+      </c>
+      <c r="O13" t="b">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>1</v>
+      </c>
+      <c r="Q13">
+        <v>30</v>
+      </c>
+      <c r="R13">
+        <v>1.75</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0.8</v>
+      </c>
+      <c r="U13">
+        <v>0.5</v>
+      </c>
+      <c r="V13" t="b">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0.8</v>
+      </c>
+      <c r="X13">
+        <v>50</v>
+      </c>
+      <c r="Y13">
+        <v>50</v>
+      </c>
+      <c r="Z13">
+        <v>10</v>
+      </c>
+      <c r="AA13">
+        <v>3</v>
+      </c>
+      <c r="AB13">
+        <v>10</v>
+      </c>
+      <c r="AC13">
+        <v>50</v>
+      </c>
+      <c r="AD13">
+        <v>82</v>
+      </c>
+      <c r="AE13">
+        <v>300</v>
+      </c>
+      <c r="AF13">
+        <v>30</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH13">
+        <v>20</v>
+      </c>
+      <c r="AI13">
+        <v>3</v>
+      </c>
+      <c r="AJ13">
+        <v>0.8</v>
+      </c>
+      <c r="AK13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW13" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="14" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E14" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" t="s">
+        <v>9</v>
+      </c>
+      <c r="H14">
+        <v>2</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" t="s">
+        <v>28</v>
+      </c>
+      <c r="L14" t="s">
+        <v>29</v>
+      </c>
+      <c r="M14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N14">
+        <v>300</v>
+      </c>
+      <c r="O14" t="b">
+        <v>1</v>
+      </c>
+      <c r="P14">
+        <v>1</v>
+      </c>
+      <c r="Q14">
+        <v>30</v>
+      </c>
+      <c r="R14">
+        <v>1.75</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0.8</v>
+      </c>
+      <c r="U14">
+        <v>0.5</v>
+      </c>
+      <c r="V14" t="b">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0.8</v>
+      </c>
+      <c r="X14">
+        <v>50</v>
+      </c>
+      <c r="Y14">
+        <v>50</v>
+      </c>
+      <c r="Z14">
+        <v>10</v>
+      </c>
+      <c r="AA14">
+        <v>3</v>
+      </c>
+      <c r="AB14">
+        <v>10</v>
+      </c>
+      <c r="AC14">
+        <v>50</v>
+      </c>
+      <c r="AD14">
+        <v>82</v>
+      </c>
+      <c r="AE14">
+        <v>300</v>
+      </c>
+      <c r="AF14">
+        <v>30</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH14">
+        <v>20</v>
+      </c>
+      <c r="AI14">
+        <v>3</v>
+      </c>
+      <c r="AJ14">
+        <v>0.8</v>
+      </c>
+      <c r="AK14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW14" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="15" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" t="s">
+        <v>94</v>
+      </c>
+      <c r="D15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E15" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15">
+        <v>2</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15" t="s">
+        <v>28</v>
+      </c>
+      <c r="L15" t="s">
+        <v>29</v>
+      </c>
+      <c r="M15" t="s">
+        <v>54</v>
+      </c>
+      <c r="N15">
+        <v>300</v>
+      </c>
+      <c r="O15" t="b">
+        <v>1</v>
+      </c>
+      <c r="P15">
+        <v>1</v>
+      </c>
+      <c r="Q15">
+        <v>30</v>
+      </c>
+      <c r="R15">
+        <v>1.75</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0.8</v>
+      </c>
+      <c r="U15">
+        <v>0.5</v>
+      </c>
+      <c r="V15" t="b">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0.8</v>
+      </c>
+      <c r="X15">
+        <v>50</v>
+      </c>
+      <c r="Y15">
+        <v>50</v>
+      </c>
+      <c r="Z15">
+        <v>10</v>
+      </c>
+      <c r="AA15">
+        <v>3</v>
+      </c>
+      <c r="AB15">
+        <v>10</v>
+      </c>
+      <c r="AC15">
+        <v>50</v>
+      </c>
+      <c r="AD15">
+        <v>82</v>
+      </c>
+      <c r="AE15">
+        <v>300</v>
+      </c>
+      <c r="AF15">
+        <v>30</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH15">
+        <v>20</v>
+      </c>
+      <c r="AI15">
+        <v>3</v>
+      </c>
+      <c r="AJ15">
+        <v>0.8</v>
+      </c>
+      <c r="AK15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW15" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="16" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" t="s">
+        <v>9</v>
+      </c>
+      <c r="H16">
+        <v>2</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
+      <c r="K16" t="s">
+        <v>28</v>
+      </c>
+      <c r="L16" t="s">
+        <v>29</v>
+      </c>
+      <c r="M16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N16">
+        <v>300</v>
+      </c>
+      <c r="O16" t="b">
+        <v>1</v>
+      </c>
+      <c r="P16">
+        <v>1</v>
+      </c>
+      <c r="Q16">
+        <v>30</v>
+      </c>
+      <c r="R16">
+        <v>1.75</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0.8</v>
+      </c>
+      <c r="U16">
+        <v>0.5</v>
+      </c>
+      <c r="V16" t="b">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0.8</v>
+      </c>
+      <c r="X16">
+        <v>50</v>
+      </c>
+      <c r="Y16">
+        <v>50</v>
+      </c>
+      <c r="Z16">
+        <v>10</v>
+      </c>
+      <c r="AA16">
+        <v>3</v>
+      </c>
+      <c r="AB16">
+        <v>10</v>
+      </c>
+      <c r="AC16">
+        <v>50</v>
+      </c>
+      <c r="AD16">
+        <v>82</v>
+      </c>
+      <c r="AE16">
+        <v>300</v>
+      </c>
+      <c r="AF16">
+        <v>30</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH16">
+        <v>20</v>
+      </c>
+      <c r="AI16">
+        <v>3</v>
+      </c>
+      <c r="AJ16">
+        <v>0.8</v>
+      </c>
+      <c r="AK16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW16" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="17" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" t="s">
+        <v>67</v>
+      </c>
+      <c r="E17" t="str">
+        <f t="shared" ref="E17:E36" si="0">PROPER(TRUE)</f>
+        <v>True</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" s="2">
+        <v>8</v>
+      </c>
+      <c r="I17" t="str">
+        <f t="shared" ref="I17:J32" si="1">PROPER(FALSE)</f>
+        <v>False</v>
+      </c>
+      <c r="J17" t="str">
+        <f t="shared" ref="J17:J28" si="2">PROPER(TRUE)</f>
+        <v>True</v>
+      </c>
+      <c r="K17" t="s">
+        <v>28</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="M17" t="s">
+        <v>54</v>
+      </c>
+      <c r="N17" s="3">
+        <v>300</v>
+      </c>
+      <c r="O17" t="str">
+        <f t="shared" ref="O17:O28" si="3">PROPER(TRUE)</f>
+        <v>True</v>
+      </c>
+      <c r="P17" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>30</v>
+      </c>
+      <c r="R17" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="S17" t="str">
+        <f t="shared" ref="S17:S36" si="4">PROPER(FALSE)</f>
+        <v>False</v>
+      </c>
+      <c r="T17" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="U17" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="V17" t="str">
+        <f t="shared" ref="V17:V36" si="5">PROPER(FALSE)</f>
+        <v>False</v>
+      </c>
+      <c r="W17" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="X17" s="3">
+        <v>50</v>
+      </c>
+      <c r="Y17" s="3">
+        <v>50</v>
+      </c>
+      <c r="Z17" s="5">
+        <v>2</v>
+      </c>
+      <c r="AA17" s="3">
+        <v>3</v>
+      </c>
+      <c r="AB17" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC17" s="3">
+        <v>50</v>
+      </c>
+      <c r="AD17" s="3">
+        <v>82</v>
+      </c>
+      <c r="AE17" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF17" s="3">
+        <v>30</v>
+      </c>
+      <c r="AG17" t="str">
+        <f t="shared" ref="AG17:AG28" si="6">PROPER(FALSE)</f>
+        <v>False</v>
+      </c>
+      <c r="AH17" s="3">
+        <v>20</v>
+      </c>
+      <c r="AI17" s="3">
+        <v>3</v>
+      </c>
+      <c r="AJ17" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="AK17" t="str">
+        <f t="shared" ref="AK17:AK36" si="7">PROPER(FALSE)</f>
+        <v>False</v>
+      </c>
+      <c r="AL17" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM17" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN17" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO17" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP17" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ17" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR17" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS17" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT17" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU17" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV17" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW17" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="18" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18" t="str">
+        <f t="shared" si="0"/>
+        <v>True</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" t="s">
+        <v>9</v>
+      </c>
+      <c r="H18" s="6">
+        <v>8</v>
+      </c>
+      <c r="I18" t="str">
+        <f t="shared" si="1"/>
+        <v>False</v>
+      </c>
+      <c r="J18" t="str">
+        <f t="shared" si="1"/>
+        <v>False</v>
+      </c>
+      <c r="K18" t="s">
+        <v>28</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="M18" t="s">
+        <v>54</v>
+      </c>
+      <c r="N18" s="3">
+        <v>300</v>
+      </c>
+      <c r="O18" t="str">
+        <f t="shared" si="3"/>
+        <v>True</v>
+      </c>
+      <c r="P18" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>30</v>
+      </c>
+      <c r="R18" s="3">
+        <v>1</v>
+      </c>
+      <c r="S18" t="str">
+        <f t="shared" si="4"/>
+        <v>False</v>
+      </c>
+      <c r="T18" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="U18" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="V18" t="str">
+        <f t="shared" si="5"/>
+        <v>False</v>
+      </c>
+      <c r="W18" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="X18" s="3">
+        <v>50</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>50</v>
+      </c>
+      <c r="Z18" s="5">
+        <v>2</v>
+      </c>
+      <c r="AA18" s="3">
+        <v>3</v>
+      </c>
+      <c r="AB18" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC18" s="3">
+        <v>50</v>
+      </c>
+      <c r="AD18" s="3">
+        <v>82</v>
+      </c>
+      <c r="AE18" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF18" s="3">
+        <v>30</v>
+      </c>
+      <c r="AG18" t="str">
+        <f t="shared" si="6"/>
+        <v>False</v>
+      </c>
+      <c r="AH18" s="3">
+        <v>20</v>
+      </c>
+      <c r="AI18" s="3">
+        <v>3</v>
+      </c>
+      <c r="AJ18" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="AK18" t="str">
+        <f t="shared" si="7"/>
+        <v>False</v>
+      </c>
+      <c r="AL18" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM18" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN18" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO18" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP18" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ18" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR18" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS18" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT18" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU18" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV18" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW18" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="19" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" t="s">
+        <v>67</v>
+      </c>
+      <c r="E19" t="str">
+        <f t="shared" si="0"/>
+        <v>True</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" t="s">
+        <v>9</v>
+      </c>
+      <c r="H19" s="2">
+        <v>6</v>
+      </c>
+      <c r="I19" t="str">
+        <f t="shared" si="1"/>
+        <v>False</v>
+      </c>
+      <c r="J19" t="str">
+        <f t="shared" si="2"/>
+        <v>True</v>
+      </c>
+      <c r="K19" t="s">
+        <v>28</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="M19" t="s">
+        <v>54</v>
+      </c>
+      <c r="N19" s="3">
+        <v>300</v>
+      </c>
+      <c r="O19" t="str">
+        <f t="shared" si="3"/>
+        <v>True</v>
+      </c>
+      <c r="P19" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>30</v>
+      </c>
+      <c r="R19" s="3">
+        <v>1.25</v>
+      </c>
+      <c r="S19" t="str">
+        <f t="shared" si="4"/>
+        <v>False</v>
+      </c>
+      <c r="T19" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="U19" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="V19" t="str">
+        <f t="shared" si="5"/>
+        <v>False</v>
+      </c>
+      <c r="W19" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="X19" s="3">
+        <v>50</v>
+      </c>
+      <c r="Y19" s="3">
+        <v>50</v>
+      </c>
+      <c r="Z19" s="5">
+        <v>2</v>
+      </c>
+      <c r="AA19" s="3">
+        <v>3</v>
+      </c>
+      <c r="AB19" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC19" s="3">
+        <v>50</v>
+      </c>
+      <c r="AD19" s="3">
+        <v>82</v>
+      </c>
+      <c r="AE19" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF19" s="3">
+        <v>30</v>
+      </c>
+      <c r="AG19" t="str">
+        <f t="shared" si="6"/>
+        <v>False</v>
+      </c>
+      <c r="AH19" s="3">
+        <v>20</v>
+      </c>
+      <c r="AI19" s="3">
+        <v>3</v>
+      </c>
+      <c r="AJ19" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="AK19" t="str">
+        <f t="shared" si="7"/>
+        <v>False</v>
+      </c>
+      <c r="AL19" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM19" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN19" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO19" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP19" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ19" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR19" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS19" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT19" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU19" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV19" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW19" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="20" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C20" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" t="s">
+        <v>67</v>
+      </c>
+      <c r="E20" t="str">
+        <f t="shared" si="0"/>
+        <v>True</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" t="s">
+        <v>9</v>
+      </c>
+      <c r="H20" s="2">
+        <v>8</v>
+      </c>
+      <c r="I20" t="str">
+        <f t="shared" si="1"/>
+        <v>False</v>
+      </c>
+      <c r="J20" t="str">
+        <f t="shared" si="2"/>
+        <v>True</v>
+      </c>
+      <c r="K20" t="s">
+        <v>28</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="M20" t="s">
+        <v>54</v>
+      </c>
+      <c r="N20" s="3">
+        <v>300</v>
+      </c>
+      <c r="O20" t="str">
+        <f t="shared" si="3"/>
+        <v>True</v>
+      </c>
+      <c r="P20" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>30</v>
+      </c>
+      <c r="R20" s="3">
+        <v>1</v>
+      </c>
+      <c r="S20" t="str">
+        <f t="shared" si="4"/>
+        <v>False</v>
+      </c>
+      <c r="T20" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="U20" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="V20" t="str">
+        <f t="shared" si="5"/>
+        <v>False</v>
+      </c>
+      <c r="W20" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="X20" s="3">
+        <v>50</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>50</v>
+      </c>
+      <c r="Z20" s="5">
+        <v>2</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>3</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC20" s="3">
+        <v>50</v>
+      </c>
+      <c r="AD20" s="3">
+        <v>82</v>
+      </c>
+      <c r="AE20" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF20" s="3">
+        <v>30</v>
+      </c>
+      <c r="AG20" t="str">
+        <f t="shared" si="6"/>
+        <v>False</v>
+      </c>
+      <c r="AH20" s="3">
+        <v>20</v>
+      </c>
+      <c r="AI20" s="3">
+        <v>3</v>
+      </c>
+      <c r="AJ20" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="AK20" t="str">
+        <f t="shared" si="7"/>
+        <v>False</v>
+      </c>
+      <c r="AL20" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM20" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN20" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO20" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP20" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ20" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR20" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS20" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT20" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU20" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV20" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW20" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="21" spans="1:49" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" t="s">
+        <v>70</v>
+      </c>
+      <c r="E21" t="str">
+        <f t="shared" si="0"/>
+        <v>True</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" t="s">
+        <v>9</v>
+      </c>
+      <c r="H21" s="2">
+        <v>8</v>
+      </c>
+      <c r="I21" t="str">
+        <f t="shared" si="1"/>
+        <v>False</v>
+      </c>
+      <c r="J21" t="str">
+        <f t="shared" si="1"/>
+        <v>False</v>
+      </c>
+      <c r="K21" t="s">
+        <v>28</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="M21" t="s">
+        <v>54</v>
+      </c>
+      <c r="N21" s="3">
+        <v>300</v>
+      </c>
+      <c r="O21" t="str">
+        <f t="shared" si="3"/>
+        <v>True</v>
+      </c>
+      <c r="P21" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>30</v>
+      </c>
+      <c r="R21" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="S21" t="str">
+        <f t="shared" si="4"/>
+        <v>False</v>
+      </c>
+      <c r="T21" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="U21" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="V21" t="str">
+        <f t="shared" si="5"/>
+        <v>False</v>
+      </c>
+      <c r="W21" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="X21" s="3">
+        <v>50</v>
+      </c>
+      <c r="Y21" s="3">
+        <v>50</v>
+      </c>
+      <c r="Z21" s="5">
+        <v>2</v>
+      </c>
+      <c r="AA21" s="3">
+        <v>3</v>
+      </c>
+      <c r="AB21" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC21" s="3">
+        <v>50</v>
+      </c>
+      <c r="AD21" s="3">
+        <v>82</v>
+      </c>
+      <c r="AE21" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF21" s="3">
+        <v>30</v>
+      </c>
+      <c r="AG21" t="str">
+        <f t="shared" si="6"/>
+        <v>False</v>
+      </c>
+      <c r="AH21" s="3">
+        <v>20</v>
+      </c>
+      <c r="AI21" s="3">
+        <v>3</v>
+      </c>
+      <c r="AJ21" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="AK21" t="str">
+        <f t="shared" si="7"/>
+        <v>False</v>
+      </c>
+      <c r="AL21" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM21" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN21" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO21" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP21" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ21" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR21" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS21" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT21" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU21" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV21" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW21" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="22" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" t="s">
+        <v>67</v>
+      </c>
+      <c r="E22" t="str">
+        <f t="shared" si="0"/>
+        <v>True</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" t="s">
+        <v>9</v>
+      </c>
+      <c r="H22" s="2">
+        <v>8</v>
+      </c>
+      <c r="I22" t="str">
+        <f t="shared" si="1"/>
+        <v>False</v>
+      </c>
+      <c r="J22" t="str">
+        <f t="shared" si="2"/>
+        <v>True</v>
+      </c>
+      <c r="K22" t="s">
+        <v>28</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="M22" t="s">
+        <v>54</v>
+      </c>
+      <c r="N22" s="3">
+        <v>300</v>
+      </c>
+      <c r="O22" t="str">
+        <f t="shared" si="3"/>
+        <v>True</v>
+      </c>
+      <c r="P22" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>30</v>
+      </c>
+      <c r="R22" s="3">
+        <v>1</v>
+      </c>
+      <c r="S22" t="str">
+        <f t="shared" si="4"/>
+        <v>False</v>
+      </c>
+      <c r="T22" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="U22" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="V22" t="str">
+        <f t="shared" si="5"/>
+        <v>False</v>
+      </c>
+      <c r="W22" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="X22" s="3">
+        <v>50</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>50</v>
+      </c>
+      <c r="Z22" s="5">
+        <v>2</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>3</v>
+      </c>
+      <c r="AB22" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC22" s="3">
+        <v>50</v>
+      </c>
+      <c r="AD22" s="3">
+        <v>82</v>
+      </c>
+      <c r="AE22" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF22" s="3">
+        <v>30</v>
+      </c>
+      <c r="AG22" t="str">
+        <f t="shared" si="6"/>
+        <v>False</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>20</v>
+      </c>
+      <c r="AI22" s="3">
+        <v>3</v>
+      </c>
+      <c r="AJ22" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="AK22" t="str">
+        <f t="shared" si="7"/>
+        <v>False</v>
+      </c>
+      <c r="AL22" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM22" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN22" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO22" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP22" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ22" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR22" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS22" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT22" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU22" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV22" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW22" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="23" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" t="s">
+        <v>35</v>
+      </c>
+      <c r="D23" t="s">
+        <v>70</v>
+      </c>
+      <c r="E23" t="str">
+        <f t="shared" si="0"/>
+        <v>True</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" t="s">
+        <v>9</v>
+      </c>
+      <c r="H23" s="2">
+        <v>8</v>
+      </c>
+      <c r="I23" t="str">
+        <f t="shared" si="1"/>
+        <v>False</v>
+      </c>
+      <c r="J23" t="str">
+        <f t="shared" si="1"/>
+        <v>False</v>
+      </c>
+      <c r="K23" t="s">
+        <v>28</v>
+      </c>
+      <c r="L23" t="s">
+        <v>29</v>
+      </c>
+      <c r="M23" t="s">
+        <v>54</v>
+      </c>
+      <c r="N23" s="3">
+        <v>300</v>
+      </c>
+      <c r="O23" t="str">
+        <f t="shared" si="3"/>
+        <v>True</v>
+      </c>
+      <c r="P23" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>30</v>
+      </c>
+      <c r="R23" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="S23" t="str">
+        <f t="shared" si="4"/>
+        <v>False</v>
+      </c>
+      <c r="T23" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="U23" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="V23" t="str">
+        <f t="shared" si="5"/>
+        <v>False</v>
+      </c>
+      <c r="W23" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="X23" s="3">
+        <v>50</v>
+      </c>
+      <c r="Y23" s="3">
+        <v>50</v>
+      </c>
+      <c r="Z23" s="5">
+        <v>2</v>
+      </c>
+      <c r="AA23" s="3">
+        <v>3</v>
+      </c>
+      <c r="AB23" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC23" s="3">
+        <v>50</v>
+      </c>
+      <c r="AD23" s="3">
+        <v>82</v>
+      </c>
+      <c r="AE23" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF23" s="3">
+        <v>30</v>
+      </c>
+      <c r="AG23" t="str">
+        <f t="shared" si="6"/>
+        <v>False</v>
+      </c>
+      <c r="AH23" s="3">
+        <v>20</v>
+      </c>
+      <c r="AI23" s="3">
+        <v>3</v>
+      </c>
+      <c r="AJ23" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="AK23" t="str">
+        <f t="shared" si="7"/>
+        <v>False</v>
+      </c>
+      <c r="AL23" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM23" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN23" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO23" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP23" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ23" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR23" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS23" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT23" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU23" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV23" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW23" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="24" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C24" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24" t="s">
+        <v>67</v>
+      </c>
+      <c r="E24" t="str">
+        <f t="shared" si="0"/>
+        <v>True</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" t="s">
+        <v>9</v>
+      </c>
+      <c r="H24" s="2">
+        <v>2</v>
+      </c>
+      <c r="I24" t="str">
+        <f t="shared" si="1"/>
+        <v>False</v>
+      </c>
+      <c r="J24" t="str">
+        <f t="shared" si="2"/>
+        <v>True</v>
+      </c>
+      <c r="K24" t="s">
+        <v>28</v>
+      </c>
+      <c r="L24" t="s">
+        <v>29</v>
+      </c>
+      <c r="M24" t="s">
+        <v>54</v>
+      </c>
+      <c r="N24" s="3">
+        <v>300</v>
+      </c>
+      <c r="O24" t="str">
+        <f t="shared" si="3"/>
+        <v>True</v>
+      </c>
+      <c r="P24" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>30</v>
+      </c>
+      <c r="R24" s="3">
+        <v>1</v>
+      </c>
+      <c r="S24" t="str">
+        <f t="shared" si="4"/>
+        <v>False</v>
+      </c>
+      <c r="T24" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="U24" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="V24" t="str">
+        <f t="shared" si="5"/>
+        <v>False</v>
+      </c>
+      <c r="W24" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="X24" s="3">
+        <v>50</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>50</v>
+      </c>
+      <c r="Z24" s="5">
+        <v>2</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>3</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>50</v>
+      </c>
+      <c r="AD24" s="3">
+        <v>82</v>
+      </c>
+      <c r="AE24" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF24" s="3">
+        <v>30</v>
+      </c>
+      <c r="AG24" t="str">
+        <f t="shared" si="6"/>
+        <v>False</v>
+      </c>
+      <c r="AH24" s="3">
+        <v>20</v>
+      </c>
+      <c r="AI24" s="3">
+        <v>3</v>
+      </c>
+      <c r="AJ24" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="AK24" t="str">
+        <f t="shared" si="7"/>
+        <v>False</v>
+      </c>
+      <c r="AL24" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM24" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN24" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO24" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP24" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ24" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR24" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS24" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT24" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU24" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV24" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW24" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="25" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" t="s">
+        <v>70</v>
+      </c>
+      <c r="E25" t="str">
+        <f t="shared" si="0"/>
+        <v>True</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" t="s">
+        <v>9</v>
+      </c>
+      <c r="H25" s="2">
+        <v>8</v>
+      </c>
+      <c r="I25" t="str">
+        <f t="shared" si="1"/>
+        <v>False</v>
+      </c>
+      <c r="J25" t="str">
+        <f t="shared" si="1"/>
+        <v>False</v>
+      </c>
+      <c r="K25" t="s">
+        <v>28</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="M25" t="s">
+        <v>54</v>
+      </c>
+      <c r="N25" s="3">
+        <v>300</v>
+      </c>
+      <c r="O25" t="str">
+        <f t="shared" si="3"/>
+        <v>True</v>
+      </c>
+      <c r="P25" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>30</v>
+      </c>
+      <c r="R25" s="3">
+        <v>1</v>
+      </c>
+      <c r="S25" t="str">
+        <f t="shared" si="4"/>
+        <v>False</v>
+      </c>
+      <c r="T25" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="U25" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="V25" t="str">
+        <f t="shared" si="5"/>
+        <v>False</v>
+      </c>
+      <c r="W25" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="X25" s="3">
+        <v>50</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>50</v>
+      </c>
+      <c r="Z25" s="5">
+        <v>2</v>
+      </c>
+      <c r="AA25" s="3">
+        <v>3</v>
+      </c>
+      <c r="AB25" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC25" s="3">
+        <v>50</v>
+      </c>
+      <c r="AD25" s="3">
+        <v>82</v>
+      </c>
+      <c r="AE25" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF25" s="3">
+        <v>30</v>
+      </c>
+      <c r="AG25" t="str">
+        <f t="shared" si="6"/>
+        <v>False</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>20</v>
+      </c>
+      <c r="AI25" s="3">
+        <v>3</v>
+      </c>
+      <c r="AJ25" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="AK25" t="str">
+        <f t="shared" si="7"/>
+        <v>False</v>
+      </c>
+      <c r="AL25" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM25" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN25" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO25" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP25" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ25" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR25" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS25" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT25" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU25" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV25" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW25" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="26" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" t="s">
+        <v>35</v>
+      </c>
+      <c r="D26" t="s">
+        <v>67</v>
+      </c>
+      <c r="E26" t="str">
+        <f t="shared" si="0"/>
+        <v>True</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" t="s">
+        <v>9</v>
+      </c>
+      <c r="H26" s="2">
+        <v>8</v>
+      </c>
+      <c r="I26" t="str">
+        <f t="shared" si="1"/>
+        <v>False</v>
+      </c>
+      <c r="J26" t="str">
+        <f t="shared" si="2"/>
+        <v>True</v>
+      </c>
+      <c r="K26" t="s">
+        <v>28</v>
+      </c>
+      <c r="L26" t="s">
+        <v>29</v>
+      </c>
+      <c r="M26" t="s">
+        <v>54</v>
+      </c>
+      <c r="N26" s="3">
+        <v>300</v>
+      </c>
+      <c r="O26" t="str">
+        <f t="shared" si="3"/>
+        <v>True</v>
+      </c>
+      <c r="P26" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>30</v>
+      </c>
+      <c r="R26" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="S26" t="str">
+        <f t="shared" si="4"/>
+        <v>False</v>
+      </c>
+      <c r="T26" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="U26" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="V26" t="str">
+        <f t="shared" si="5"/>
+        <v>False</v>
+      </c>
+      <c r="W26" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="X26" s="3">
+        <v>50</v>
+      </c>
+      <c r="Y26" s="3">
+        <v>50</v>
+      </c>
+      <c r="Z26" s="5">
+        <v>2</v>
+      </c>
+      <c r="AA26" s="3">
+        <v>3</v>
+      </c>
+      <c r="AB26" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC26" s="3">
+        <v>50</v>
+      </c>
+      <c r="AD26" s="3">
+        <v>82</v>
+      </c>
+      <c r="AE26" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF26" s="3">
+        <v>30</v>
+      </c>
+      <c r="AG26" t="str">
+        <f t="shared" si="6"/>
+        <v>False</v>
+      </c>
+      <c r="AH26" s="3">
+        <v>20</v>
+      </c>
+      <c r="AI26" s="3">
+        <v>3</v>
+      </c>
+      <c r="AJ26" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="AK26" t="str">
+        <f t="shared" si="7"/>
+        <v>False</v>
+      </c>
+      <c r="AL26" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM26" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN26" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO26" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP26" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ26" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR26" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS26" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT26" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU26" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV26" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW26" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="27" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C27" t="s">
+        <v>44</v>
+      </c>
+      <c r="D27" t="s">
+        <v>80</v>
+      </c>
+      <c r="E27" t="str">
+        <f t="shared" si="0"/>
+        <v>True</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" t="s">
+        <v>9</v>
+      </c>
+      <c r="H27" s="2">
+        <v>2</v>
+      </c>
+      <c r="I27" t="str">
+        <f t="shared" si="1"/>
+        <v>False</v>
+      </c>
+      <c r="J27" t="str">
+        <f t="shared" si="2"/>
+        <v>True</v>
+      </c>
+      <c r="K27" t="s">
+        <v>28</v>
+      </c>
+      <c r="L27" t="s">
+        <v>29</v>
+      </c>
+      <c r="M27" t="s">
+        <v>54</v>
+      </c>
+      <c r="N27" s="3">
+        <v>300</v>
+      </c>
+      <c r="O27" t="str">
+        <f t="shared" si="3"/>
+        <v>True</v>
+      </c>
+      <c r="P27" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>30</v>
+      </c>
+      <c r="R27" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="S27" t="str">
+        <f t="shared" si="4"/>
+        <v>False</v>
+      </c>
+      <c r="T27" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="U27" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="V27" t="str">
+        <f t="shared" si="5"/>
+        <v>False</v>
+      </c>
+      <c r="W27" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="X27" s="3">
+        <v>50</v>
+      </c>
+      <c r="Y27" s="3">
+        <v>50</v>
+      </c>
+      <c r="Z27" s="5">
+        <v>2</v>
+      </c>
+      <c r="AA27" s="3">
+        <v>3</v>
+      </c>
+      <c r="AB27" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC27" s="3">
+        <v>50</v>
+      </c>
+      <c r="AD27" s="3">
+        <v>82</v>
+      </c>
+      <c r="AE27" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF27" s="3">
+        <v>30</v>
+      </c>
+      <c r="AG27" t="str">
+        <f t="shared" si="6"/>
+        <v>False</v>
+      </c>
+      <c r="AH27" s="3">
+        <v>20</v>
+      </c>
+      <c r="AI27" s="3">
+        <v>3</v>
+      </c>
+      <c r="AJ27" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="AK27" t="str">
+        <f t="shared" si="7"/>
+        <v>False</v>
+      </c>
+      <c r="AL27" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM27" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN27" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO27" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP27" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ27" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR27" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS27" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT27" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU27" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV27" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW27" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="28" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" t="s">
+        <v>35</v>
+      </c>
+      <c r="D28" t="s">
+        <v>67</v>
+      </c>
+      <c r="E28" t="str">
+        <f t="shared" si="0"/>
+        <v>True</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28" t="s">
+        <v>9</v>
+      </c>
+      <c r="H28" s="2">
+        <v>8</v>
+      </c>
+      <c r="I28" t="str">
+        <f t="shared" si="1"/>
+        <v>False</v>
+      </c>
+      <c r="J28" t="str">
+        <f t="shared" si="2"/>
+        <v>True</v>
+      </c>
+      <c r="K28" t="s">
+        <v>28</v>
+      </c>
+      <c r="L28" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="M28" t="s">
+        <v>54</v>
+      </c>
+      <c r="N28" s="3">
+        <v>300</v>
+      </c>
+      <c r="O28" t="str">
+        <f t="shared" si="3"/>
+        <v>True</v>
+      </c>
+      <c r="P28" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>30</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="S28" t="str">
+        <f t="shared" si="4"/>
+        <v>False</v>
+      </c>
+      <c r="T28" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="U28" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="V28" t="str">
+        <f t="shared" si="5"/>
+        <v>False</v>
+      </c>
+      <c r="W28" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="X28" s="3">
+        <v>50</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>50</v>
+      </c>
+      <c r="Z28" s="5">
+        <v>2</v>
+      </c>
+      <c r="AA28" s="3">
+        <v>3</v>
+      </c>
+      <c r="AB28" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC28" s="3">
+        <v>50</v>
+      </c>
+      <c r="AD28" s="3">
+        <v>82</v>
+      </c>
+      <c r="AE28" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF28" s="3">
+        <v>30</v>
+      </c>
+      <c r="AG28" t="str">
+        <f t="shared" si="6"/>
+        <v>False</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>20</v>
+      </c>
+      <c r="AI28" s="3">
+        <v>3</v>
+      </c>
+      <c r="AJ28" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="AK28" t="str">
+        <f t="shared" si="7"/>
+        <v>False</v>
+      </c>
+      <c r="AL28" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM28" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN28" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO28" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP28" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ28" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR28" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS28" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT28" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU28" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV28" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW28" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="29" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B29" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" t="s">
+        <v>44</v>
+      </c>
+      <c r="D29" t="e">
+        <f>#N/A</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E29" t="str">
+        <f>PROPER(FALSE)</f>
+        <v>False</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29" t="s">
+        <v>9</v>
+      </c>
+      <c r="H29" s="2">
+        <v>8</v>
+      </c>
+      <c r="I29" t="str">
+        <f t="shared" si="1"/>
+        <v>False</v>
+      </c>
+      <c r="J29" t="str">
+        <f t="shared" si="1"/>
+        <v>False</v>
+      </c>
+      <c r="K29" t="s">
+        <v>28</v>
+      </c>
+      <c r="L29" t="s">
+        <v>29</v>
+      </c>
+      <c r="M29" t="s">
+        <v>54</v>
+      </c>
+      <c r="N29" s="3">
+        <v>300</v>
+      </c>
+      <c r="O29" t="str">
+        <f t="shared" ref="O29:O31" si="8">PROPER(FALSE)</f>
+        <v>False</v>
+      </c>
+      <c r="P29" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>30</v>
+      </c>
+      <c r="R29" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="S29" t="str">
+        <f t="shared" si="4"/>
+        <v>False</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="V29" t="str">
+        <f t="shared" si="5"/>
+        <v>False</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="X29" s="3">
+        <v>50</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>50</v>
+      </c>
+      <c r="Z29" s="5">
+        <v>2</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>3</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>50</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>82</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF29" s="3">
+        <v>30</v>
+      </c>
+      <c r="AG29" t="str">
+        <f t="shared" ref="AG29:AG31" si="9">PROPER(TRUE)</f>
+        <v>True</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>20</v>
+      </c>
+      <c r="AI29" s="3">
+        <v>3</v>
+      </c>
+      <c r="AJ29" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="AK29" t="str">
+        <f t="shared" si="7"/>
+        <v>False</v>
+      </c>
+      <c r="AL29" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM29" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN29" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO29" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP29" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ29" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR29" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS29" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT29" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU29" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV29" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW29" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="30" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B30" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" t="s">
+        <v>44</v>
+      </c>
+      <c r="D30" t="e">
+        <f>#N/A</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E30" t="str">
+        <f>PROPER(FALSE)</f>
+        <v>False</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30" t="s">
+        <v>9</v>
+      </c>
+      <c r="H30" s="2">
+        <v>8</v>
+      </c>
+      <c r="I30" t="str">
+        <f t="shared" si="1"/>
+        <v>False</v>
+      </c>
+      <c r="J30" t="str">
+        <f t="shared" si="1"/>
+        <v>False</v>
+      </c>
+      <c r="K30" t="s">
+        <v>84</v>
+      </c>
+      <c r="L30" t="s">
+        <v>29</v>
+      </c>
+      <c r="M30" t="s">
+        <v>54</v>
+      </c>
+      <c r="N30" s="3">
+        <v>300</v>
+      </c>
+      <c r="O30" t="str">
+        <f t="shared" si="8"/>
+        <v>False</v>
+      </c>
+      <c r="P30" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>30</v>
+      </c>
+      <c r="R30" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="S30" t="str">
+        <f t="shared" si="4"/>
+        <v>False</v>
+      </c>
+      <c r="T30" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="U30" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="V30" t="str">
+        <f t="shared" si="5"/>
+        <v>False</v>
+      </c>
+      <c r="W30" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="X30" s="3">
+        <v>50</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>50</v>
+      </c>
+      <c r="Z30" s="5">
+        <v>2</v>
+      </c>
+      <c r="AA30" s="3">
+        <v>3</v>
+      </c>
+      <c r="AB30" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC30" s="3">
+        <v>50</v>
+      </c>
+      <c r="AD30" s="3">
+        <v>82</v>
+      </c>
+      <c r="AE30" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF30" s="3">
+        <v>30</v>
+      </c>
+      <c r="AG30" t="str">
+        <f t="shared" si="9"/>
+        <v>True</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>20</v>
+      </c>
+      <c r="AI30" s="3">
+        <v>3</v>
+      </c>
+      <c r="AJ30" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="AK30" t="str">
+        <f t="shared" si="7"/>
+        <v>False</v>
+      </c>
+      <c r="AL30" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM30" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN30" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO30" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP30" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ30" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR30" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS30" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT30" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU30" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV30" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW30" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="31" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31" t="s">
+        <v>44</v>
+      </c>
+      <c r="D31" t="e">
+        <f>#N/A</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E31" t="str">
+        <f>PROPER(FALSE)</f>
+        <v>False</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31" t="s">
+        <v>9</v>
+      </c>
+      <c r="H31" s="2">
+        <v>8</v>
+      </c>
+      <c r="I31" t="str">
+        <f t="shared" si="1"/>
+        <v>False</v>
+      </c>
+      <c r="J31" t="str">
+        <f t="shared" si="1"/>
+        <v>False</v>
+      </c>
+      <c r="K31" t="s">
+        <v>84</v>
+      </c>
+      <c r="L31" t="s">
+        <v>29</v>
+      </c>
+      <c r="M31" t="s">
+        <v>54</v>
+      </c>
+      <c r="N31" s="3">
+        <v>300</v>
+      </c>
+      <c r="O31" t="str">
+        <f t="shared" si="8"/>
+        <v>False</v>
+      </c>
+      <c r="P31" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>30</v>
+      </c>
+      <c r="R31" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="S31" t="str">
+        <f t="shared" si="4"/>
+        <v>False</v>
+      </c>
+      <c r="T31" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="U31" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="V31" t="str">
+        <f t="shared" si="5"/>
+        <v>False</v>
+      </c>
+      <c r="W31" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="X31" s="3">
+        <v>50</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>50</v>
+      </c>
+      <c r="Z31" s="5">
+        <v>2</v>
+      </c>
+      <c r="AA31" s="3">
+        <v>3</v>
+      </c>
+      <c r="AB31" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC31" s="3">
+        <v>50</v>
+      </c>
+      <c r="AD31" s="3">
+        <v>82</v>
+      </c>
+      <c r="AE31" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF31" s="3">
+        <v>30</v>
+      </c>
+      <c r="AG31" t="str">
+        <f t="shared" si="9"/>
+        <v>True</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>20</v>
+      </c>
+      <c r="AI31" s="3">
+        <v>3</v>
+      </c>
+      <c r="AJ31" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="AK31" t="str">
+        <f t="shared" si="7"/>
+        <v>False</v>
+      </c>
+      <c r="AL31" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM31" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN31" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO31" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP31" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ31" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR31" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS31" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT31" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU31" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV31" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW31" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="32" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C32" t="s">
+        <v>44</v>
+      </c>
+      <c r="D32" t="s">
+        <v>67</v>
+      </c>
+      <c r="E32" t="str">
+        <f t="shared" si="0"/>
+        <v>True</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32" t="s">
+        <v>9</v>
+      </c>
+      <c r="H32" s="2">
+        <v>4</v>
+      </c>
+      <c r="I32" t="str">
+        <f t="shared" si="1"/>
+        <v>False</v>
+      </c>
+      <c r="J32" t="str">
+        <f t="shared" ref="J32:J36" si="10">PROPER(TRUE)</f>
+        <v>True</v>
+      </c>
+      <c r="K32" t="s">
+        <v>28</v>
+      </c>
+      <c r="L32" t="s">
+        <v>29</v>
+      </c>
+      <c r="M32" t="s">
+        <v>54</v>
+      </c>
+      <c r="N32" s="3">
+        <v>300</v>
+      </c>
+      <c r="O32" t="str">
+        <f t="shared" ref="O32:O36" si="11">PROPER(TRUE)</f>
+        <v>True</v>
+      </c>
+      <c r="P32" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>30</v>
+      </c>
+      <c r="R32" s="3">
+        <v>1</v>
+      </c>
+      <c r="S32" t="str">
+        <f t="shared" si="4"/>
+        <v>False</v>
+      </c>
+      <c r="T32" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="U32" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="V32" t="str">
+        <f t="shared" si="5"/>
+        <v>False</v>
+      </c>
+      <c r="W32" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="X32" s="3">
+        <v>50</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>50</v>
+      </c>
+      <c r="Z32" s="5">
+        <v>2</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>3</v>
+      </c>
+      <c r="AB32" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC32" s="3">
+        <v>50</v>
+      </c>
+      <c r="AD32" s="3">
+        <v>82</v>
+      </c>
+      <c r="AE32" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF32" s="3">
+        <v>30</v>
+      </c>
+      <c r="AG32" t="str">
+        <f t="shared" ref="AG32:AG36" si="12">PROPER(FALSE)</f>
+        <v>False</v>
+      </c>
+      <c r="AH32" s="3">
+        <v>20</v>
+      </c>
+      <c r="AI32" s="3">
+        <v>3</v>
+      </c>
+      <c r="AJ32" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="AK32" t="str">
+        <f t="shared" si="7"/>
+        <v>False</v>
+      </c>
+      <c r="AL32" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM32" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN32" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO32" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP32" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ32" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR32" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS32" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT32" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU32" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV32" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW32" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="33" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C33" t="s">
+        <v>44</v>
+      </c>
+      <c r="D33" t="s">
+        <v>88</v>
+      </c>
+      <c r="E33" t="str">
+        <f t="shared" si="0"/>
+        <v>True</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G33" t="s">
+        <v>9</v>
+      </c>
+      <c r="H33" s="2">
+        <v>2</v>
+      </c>
+      <c r="I33" t="str">
+        <f t="shared" ref="I33:I36" si="13">PROPER(FALSE)</f>
+        <v>False</v>
+      </c>
+      <c r="J33" t="str">
+        <f t="shared" si="10"/>
+        <v>True</v>
+      </c>
+      <c r="K33" t="s">
+        <v>28</v>
+      </c>
+      <c r="L33" t="s">
+        <v>29</v>
+      </c>
+      <c r="M33" t="s">
+        <v>54</v>
+      </c>
+      <c r="N33" s="3">
+        <v>300</v>
+      </c>
+      <c r="O33" t="str">
+        <f t="shared" si="11"/>
+        <v>True</v>
+      </c>
+      <c r="P33" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>30</v>
+      </c>
+      <c r="R33" s="3">
+        <v>1.75</v>
+      </c>
+      <c r="S33" t="str">
+        <f t="shared" si="4"/>
+        <v>False</v>
+      </c>
+      <c r="T33" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="U33" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="V33" t="str">
+        <f t="shared" si="5"/>
+        <v>False</v>
+      </c>
+      <c r="W33" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="X33" s="3">
+        <v>50</v>
+      </c>
+      <c r="Y33" s="3">
+        <v>50</v>
+      </c>
+      <c r="Z33" s="5">
+        <v>2</v>
+      </c>
+      <c r="AA33" s="3">
+        <v>3</v>
+      </c>
+      <c r="AB33" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC33" s="3">
+        <v>50</v>
+      </c>
+      <c r="AD33" s="3">
+        <v>82</v>
+      </c>
+      <c r="AE33" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF33" s="3">
+        <v>30</v>
+      </c>
+      <c r="AG33" t="str">
+        <f t="shared" si="12"/>
+        <v>False</v>
+      </c>
+      <c r="AH33" s="3">
+        <v>20</v>
+      </c>
+      <c r="AI33" s="3">
+        <v>3</v>
+      </c>
+      <c r="AJ33" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="AK33" t="str">
+        <f t="shared" si="7"/>
+        <v>False</v>
+      </c>
+      <c r="AL33" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM33" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN33" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO33" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP33" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ33" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR33" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS33" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT33" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU33" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV33" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW33" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="34" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C34" t="s">
+        <v>44</v>
+      </c>
+      <c r="D34" t="s">
+        <v>88</v>
+      </c>
+      <c r="E34" t="str">
+        <f t="shared" si="0"/>
+        <v>True</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G34" t="s">
+        <v>9</v>
+      </c>
+      <c r="H34" s="2">
+        <v>2</v>
+      </c>
+      <c r="I34" t="str">
+        <f t="shared" si="13"/>
+        <v>False</v>
+      </c>
+      <c r="J34" t="str">
+        <f t="shared" si="10"/>
+        <v>True</v>
+      </c>
+      <c r="K34" t="s">
+        <v>28</v>
+      </c>
+      <c r="L34" t="s">
+        <v>29</v>
+      </c>
+      <c r="M34" t="s">
+        <v>54</v>
+      </c>
+      <c r="N34" s="3">
+        <v>300</v>
+      </c>
+      <c r="O34" t="str">
+        <f t="shared" si="11"/>
+        <v>True</v>
+      </c>
+      <c r="P34" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>30</v>
+      </c>
+      <c r="R34" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="S34" t="str">
+        <f t="shared" si="4"/>
+        <v>False</v>
+      </c>
+      <c r="T34" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="U34" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="V34" t="str">
+        <f t="shared" si="5"/>
+        <v>False</v>
+      </c>
+      <c r="W34" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="X34" s="3">
+        <v>50</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>50</v>
+      </c>
+      <c r="Z34" s="5">
+        <v>2</v>
+      </c>
+      <c r="AA34" s="3">
+        <v>3</v>
+      </c>
+      <c r="AB34" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC34" s="3">
+        <v>50</v>
+      </c>
+      <c r="AD34" s="3">
+        <v>82</v>
+      </c>
+      <c r="AE34" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF34" s="3">
+        <v>30</v>
+      </c>
+      <c r="AG34" t="str">
+        <f t="shared" si="12"/>
+        <v>False</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>20</v>
+      </c>
+      <c r="AI34" s="3">
+        <v>3</v>
+      </c>
+      <c r="AJ34" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="AK34" t="str">
+        <f t="shared" si="7"/>
+        <v>False</v>
+      </c>
+      <c r="AL34" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM34" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN34" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO34" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP34" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ34" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR34" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS34" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT34" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU34" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV34" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW34" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="35" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C35" t="s">
+        <v>91</v>
+      </c>
+      <c r="D35" t="s">
+        <v>88</v>
+      </c>
+      <c r="E35" t="str">
+        <f t="shared" si="0"/>
+        <v>True</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35" t="s">
+        <v>9</v>
+      </c>
+      <c r="H35" s="2">
+        <v>2</v>
+      </c>
+      <c r="I35" t="str">
+        <f t="shared" si="13"/>
+        <v>False</v>
+      </c>
+      <c r="J35" t="str">
+        <f t="shared" si="10"/>
+        <v>True</v>
+      </c>
+      <c r="K35" t="s">
+        <v>28</v>
+      </c>
+      <c r="L35" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="M35" t="s">
+        <v>54</v>
+      </c>
+      <c r="N35" s="3">
+        <v>300</v>
+      </c>
+      <c r="O35" t="str">
+        <f t="shared" si="11"/>
+        <v>True</v>
+      </c>
+      <c r="P35" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>30</v>
+      </c>
+      <c r="R35" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="S35" t="str">
+        <f t="shared" si="4"/>
+        <v>False</v>
+      </c>
+      <c r="T35" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="U35" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="V35" t="str">
+        <f t="shared" si="5"/>
+        <v>False</v>
+      </c>
+      <c r="W35" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="X35" s="3">
+        <v>50</v>
+      </c>
+      <c r="Y35" s="3">
+        <v>50</v>
+      </c>
+      <c r="Z35" s="5">
+        <v>1</v>
+      </c>
+      <c r="AA35" s="3">
+        <v>3</v>
+      </c>
+      <c r="AB35" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC35" s="3">
+        <v>50</v>
+      </c>
+      <c r="AD35" s="3">
+        <v>82</v>
+      </c>
+      <c r="AE35" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF35" s="3">
+        <v>30</v>
+      </c>
+      <c r="AG35" t="str">
+        <f t="shared" si="12"/>
+        <v>False</v>
+      </c>
+      <c r="AH35" s="3">
+        <v>20</v>
+      </c>
+      <c r="AI35" s="3">
+        <v>3</v>
+      </c>
+      <c r="AJ35" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="AK35" t="str">
+        <f t="shared" si="7"/>
+        <v>False</v>
+      </c>
+      <c r="AL35" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM35" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN35" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO35" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP35" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ35" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR35" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS35" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT35" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU35" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV35" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW35" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="36" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C36" t="s">
+        <v>91</v>
+      </c>
+      <c r="D36" t="s">
+        <v>93</v>
+      </c>
+      <c r="E36" t="str">
+        <f t="shared" si="0"/>
+        <v>True</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G36" t="s">
+        <v>9</v>
+      </c>
+      <c r="H36" s="2">
+        <v>2</v>
+      </c>
+      <c r="I36" t="str">
+        <f t="shared" si="13"/>
+        <v>False</v>
+      </c>
+      <c r="J36" t="str">
+        <f t="shared" si="10"/>
+        <v>True</v>
+      </c>
+      <c r="K36" t="s">
+        <v>28</v>
+      </c>
+      <c r="L36" t="s">
+        <v>29</v>
+      </c>
+      <c r="M36" t="s">
+        <v>54</v>
+      </c>
+      <c r="N36" s="3">
+        <v>300</v>
+      </c>
+      <c r="O36" t="str">
+        <f t="shared" si="11"/>
+        <v>True</v>
+      </c>
+      <c r="P36" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q36" s="3">
+        <v>30</v>
+      </c>
+      <c r="R36" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="S36" t="str">
+        <f t="shared" si="4"/>
+        <v>False</v>
+      </c>
+      <c r="T36" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="U36" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="V36" t="str">
+        <f t="shared" si="5"/>
+        <v>False</v>
+      </c>
+      <c r="W36" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="X36" s="3">
+        <v>50</v>
+      </c>
+      <c r="Y36" s="3">
+        <v>50</v>
+      </c>
+      <c r="Z36" s="5">
+        <v>1</v>
+      </c>
+      <c r="AA36" s="3">
+        <v>3</v>
+      </c>
+      <c r="AB36" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC36" s="3">
+        <v>50</v>
+      </c>
+      <c r="AD36" s="3">
+        <v>82</v>
+      </c>
+      <c r="AE36" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF36" s="3">
+        <v>30</v>
+      </c>
+      <c r="AG36" t="str">
+        <f t="shared" si="12"/>
+        <v>False</v>
+      </c>
+      <c r="AH36" s="3">
+        <v>20</v>
+      </c>
+      <c r="AI36" s="3">
+        <v>3</v>
+      </c>
+      <c r="AJ36" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="AK36" t="str">
+        <f t="shared" si="7"/>
+        <v>False</v>
+      </c>
+      <c r="AL36" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM36" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN36" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO36" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP36" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ36" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR36" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS36" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT36" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU36" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV36" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW36" s="5" t="e">
         <v>#N/A</v>
       </c>
     </row>
